--- a/Cursor/3_쿠팡 모니터링/cp_wau.xlsx
+++ b/Cursor/3_쿠팡 모니터링/cp_wau.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Cursor/coupang-monitoring-vercel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\hana\Cursor\3_쿠팡 모니터링\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B01D5B-2F73-7B41-A43E-5195E98A1E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3777D954-74CC-46FB-8D36-A33D5EB45C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1940" yWindow="1340" windowWidth="27700" windowHeight="16880" xr2:uid="{557A2CCC-BB76-854E-B723-57C8CB621632}"/>
+    <workbookView xWindow="29170" yWindow="-7960" windowWidth="17280" windowHeight="13240" xr2:uid="{557A2CCC-BB76-854E-B723-57C8CB621632}"/>
   </bookViews>
   <sheets>
     <sheet name="MI-INSIGHT1773654315714" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="51">
   <si>
     <t>모바일인덱스 INSIGHT CSV REPORT</t>
   </si>
@@ -164,13 +169,22 @@
   </si>
   <si>
     <t>2026-03-09 ~ 2026-03-15</t>
+  </si>
+  <si>
+    <t>2026-03-16 ~ 2026-03-22</t>
+  </si>
+  <si>
+    <t>2026-03-23 ~ 2026-03-29</t>
+  </si>
+  <si>
+    <t>2026-03-30 ~ 2026-04-05</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -819,9 +833,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -859,7 +873,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -965,7 +979,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1107,7 +1121,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1115,35 +1129,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8398EB-50DF-6E4C-9081-89E2B7760E95}">
-  <dimension ref="A1:E44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="24.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1160,7 +1177,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1177,7 +1194,7 @@
         <v>8242690</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1194,7 +1211,7 @@
         <v>8266969</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1211,7 +1228,7 @@
         <v>8261570</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1228,7 +1245,7 @@
         <v>8407703</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1245,7 +1262,7 @@
         <v>8228256</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1262,7 +1279,7 @@
         <v>8193626</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1279,7 +1296,7 @@
         <v>8203443</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1296,7 +1313,7 @@
         <v>8348178</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -1313,7 +1330,7 @@
         <v>8316055</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1330,7 +1347,7 @@
         <v>8559015</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -1347,7 +1364,7 @@
         <v>8373883</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1364,7 +1381,7 @@
         <v>8314386</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1381,7 +1398,7 @@
         <v>8280816</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1398,7 +1415,7 @@
         <v>8378236</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1415,7 +1432,7 @@
         <v>8392014</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1432,7 +1449,7 @@
         <v>8526316</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -1449,7 +1466,7 @@
         <v>8372067</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1466,7 +1483,7 @@
         <v>8400187</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1483,7 +1500,7 @@
         <v>8467555</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1500,7 +1517,7 @@
         <v>8481490</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1517,7 +1534,7 @@
         <v>8530831</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1534,7 +1551,7 @@
         <v>8567007</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1551,7 +1568,7 @@
         <v>9145313</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1568,7 +1585,7 @@
         <v>8408740</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -1585,7 +1602,7 @@
         <v>8279372</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -1602,7 +1619,7 @@
         <v>8122966</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -1619,7 +1636,7 @@
         <v>8161748</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -1636,7 +1653,7 @@
         <v>8313411</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -1653,7 +1670,7 @@
         <v>8462225</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -1670,7 +1687,7 @@
         <v>8493971</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -1687,7 +1704,7 @@
         <v>8419796</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -1704,7 +1721,7 @@
         <v>8375685</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -1721,7 +1738,7 @@
         <v>8416263</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -1738,7 +1755,7 @@
         <v>8469094</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -1755,7 +1772,7 @@
         <v>8649792</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1772,7 +1789,7 @@
         <v>8979524</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -1787,6 +1804,57 @@
       </c>
       <c r="E44">
         <v>8934119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45">
+        <v>28072077</v>
+      </c>
+      <c r="D45">
+        <v>19273106</v>
+      </c>
+      <c r="E45">
+        <v>8798971</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46">
+        <v>27813313</v>
+      </c>
+      <c r="D46">
+        <v>19131332</v>
+      </c>
+      <c r="E46">
+        <v>8681981</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47">
+        <v>28131956</v>
+      </c>
+      <c r="D47">
+        <v>19245431</v>
+      </c>
+      <c r="E47">
+        <v>8886525</v>
       </c>
     </row>
   </sheetData>
